--- a/DAY 1/Sourya Banerjee_TestReport.xlsx
+++ b/DAY 1/Sourya Banerjee_TestReport.xlsx
@@ -5,6 +5,10 @@
   <sheets>
     <sheet state="visible" name="User Story" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Test Scenarios" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Test Cases" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Defect Report" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="RTM" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Summary" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="258">
   <si>
     <t>Issue Type</t>
   </si>
@@ -47,7 +51,7 @@
     <t>Sub Story 2</t>
   </si>
   <si>
-    <t>Clicking Painting &amp; Cleaning redirects to the services listing page</t>
+    <t>Clicking Painting &amp; Cleaning redirects to the Home Services landing page</t>
   </si>
   <si>
     <t>Sub Story 3</t>
@@ -201,7 +205,7 @@
   </si>
   <si>
     <t>1.Validate NoBroker homepage loads successfully on entering the URL
-2.Validate Home Services option is visible on the homepage
+2.Validate Painting and Cleaning option is visible on the homepage
 3.Validate clicking Home Services redirects to the correct landing page with all service categories displayed</t>
   </si>
   <si>
@@ -245,10 +249,10 @@
     <t>Verify date and time slot selection for service booking</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Validate only future dates are selectable on the calendar
+    <t>1. Validate only future dates are selectable on the calendar
  2. Validate past dates are greyed out and unselectable
  3. Validate available time slots load on selecting a valid date
-</t>
+4. Validate user can increment quantity for the same sub-service</t>
   </si>
   <si>
     <t>TS_NB_05</t>
@@ -264,13 +268,599 @@
  2. Validate price breakdown has no hidden charges
  3. Validate user can edit service or address from summary.
  4. Validate payment page loads with all available payment options (UPI, Card, Net Banking)</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Condition</t>
+  </si>
+  <si>
+    <t>Test Case Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 1</t>
+  </si>
+  <si>
+    <t>Status Iteration 1</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2
+ (to be updated only if test case failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>Status Iteration 2
+ (to be updated only if test case failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Req. Reference</t>
+  </si>
+  <si>
+    <t>TC_NB_01_01</t>
+  </si>
+  <si>
+    <t>Browser is open and internet is available</t>
+  </si>
+  <si>
+    <t>Validate NoBroker homepage loads on entering the URL</t>
+  </si>
+  <si>
+    <t>1. Open browser
+ 2. Enter https://www.nobroker.in in address bar
+ 3. Press Enter</t>
+  </si>
+  <si>
+    <t>URL: https://www.nobroker.in</t>
+  </si>
+  <si>
+    <t>NoBroker homepage loads successfully with all sections visible</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC_NB_01_02</t>
+  </si>
+  <si>
+    <t>NoBroker homepage is loaded</t>
+  </si>
+  <si>
+    <t>Validate Painting &amp; Cleaning option is visible on the homepage</t>
+  </si>
+  <si>
+    <t>1. Scroll through the homepage
+ 2. Look for 'Painting and Cleaning' option on the navigation or homepage tiles</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Painting &amp; Cleaning option is clearly visible on the homepage</t>
+  </si>
+  <si>
+    <t>Painting &amp; Cleaning option is visible on the homepage</t>
+  </si>
+  <si>
+    <t>TC_NB_01_03</t>
+  </si>
+  <si>
+    <t>Validate clicking Painting and Cleaning redirects to the correct landing page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Painting and Cleaning' on the homepage
+ 2. Observe the page that loads</t>
+  </si>
+  <si>
+    <t>User is redirected to Home Services landing page showing Electrician, Plumber, Carpenter and other service categories</t>
+  </si>
+  <si>
+    <t>TC_NB_02_01</t>
+  </si>
+  <si>
+    <t>User is on the Home Services landing page</t>
+  </si>
+  <si>
+    <t>Validate Electrician, Plumber and Carpenter tiles are visible</t>
+  </si>
+  <si>
+    <t>1. Navigate to Home Services landing page
+ 2. Observe service tiles displayed on the page</t>
+  </si>
+  <si>
+    <t>Electrician, Plumber and Carpenter tiles are visible with correct labels and icons</t>
+  </si>
+  <si>
+    <t>TC_NB_02_02</t>
+  </si>
+  <si>
+    <t>Validate clicking a service tile navigates to the correct sub-services page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Electrician' tile
+ 2. Observe the page that loads
+ 3. Go back and repeat for Plumber and Carpenter</t>
+  </si>
+  <si>
+    <t>Service: Electrician</t>
+  </si>
+  <si>
+    <t>Clicking each tile navigates to its respective sub-services page with correct service name in heading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicking Electrician tile navigates to Electrician services page </t>
+  </si>
+  <si>
+    <t>TC_NB_02_03</t>
+  </si>
+  <si>
+    <t>User is on the Electrician/Plumber/Carpenter sub-services page</t>
+  </si>
+  <si>
+    <t>Validate all sub-services are listed with name and price</t>
+  </si>
+  <si>
+    <t>1. Navigate to any service sub-page (e.g. Electrician)
+ 2. Check that each listed service has a name and a price displayed</t>
+  </si>
+  <si>
+    <t>Service: Electrician sub-services</t>
+  </si>
+  <si>
+    <t>All sub-services are displayed with their name and price visible</t>
+  </si>
+  <si>
+    <t>TC_NB_02_04</t>
+  </si>
+  <si>
+    <t>User is on the sub-services page</t>
+  </si>
+  <si>
+    <t>Validate user can add one or multiple sub-services to the booking</t>
+  </si>
+  <si>
+    <t>1. Click 'Add' on one sub-service
+ 2. Observe cart updates
+ 3. Click 'Add' on another sub-service
+ 4. Observe cart updates again</t>
+  </si>
+  <si>
+    <t>Services: Switch Replacement + Fan Repair</t>
+  </si>
+  <si>
+    <t>Both services are added; cart count and total price update correctly; Proceed button becomes active</t>
+  </si>
+  <si>
+    <t>Order Summary with services anf total amount is visible on the right side with an activated Proceed button below</t>
+  </si>
+  <si>
+    <t>TC_NB_02_05</t>
+  </si>
+  <si>
+    <t>User is on the sub-services page with no service selected</t>
+  </si>
+  <si>
+    <t>Validate Proceed option does not appear with empty selection</t>
+  </si>
+  <si>
+    <t>1. Do not select any sub-service
+ 2. Check for Proceed button visibility or state</t>
+  </si>
+  <si>
+    <t>Cart: Empty</t>
+  </si>
+  <si>
+    <t>Proceed button is absent; user cannot move to next step without selecting a service</t>
+  </si>
+  <si>
+    <t>Proceed button is absent</t>
+  </si>
+  <si>
+    <t>TC_NB_03_01</t>
+  </si>
+  <si>
+    <t>User has selected a service and clicked Proceed</t>
+  </si>
+  <si>
+    <t>Validate user can search and select a location from the map</t>
+  </si>
+  <si>
+    <t>1. On the address page, click the location search bar
+ 2. Type area name (e.g. Indiranagar, Bangalore)
+ 3. Select area from dropdown
+ 4. Click Confirm Location</t>
+  </si>
+  <si>
+    <t>Area: Indiranagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Map pins to selected location; user is prompted to enter Flat No, Landmark and Save As</t>
+  </si>
+  <si>
+    <t>Indiranagar, Bangalore is selected on the map and user has to enter House No/Flat No, Landmark and Save As</t>
+  </si>
+  <si>
+    <t>TC_NB_03_02</t>
+  </si>
+  <si>
+    <t>User has confirmed location on map</t>
+  </si>
+  <si>
+    <t>Validate user cannot proceed when all three fields are left empty</t>
+  </si>
+  <si>
+    <t>1. Leave Flat No, Landmark fields blank. Save as is by default set at Home option
+ 2. Click Proceed</t>
+  </si>
+  <si>
+    <t>Flat No: blank | Landmark: blank | Save As: blank</t>
+  </si>
+  <si>
+    <t>Validation errors shown on empty fields; user cannot proceed to the next step</t>
+  </si>
+  <si>
+    <t>Please enter all fields' option shown on the right</t>
+  </si>
+  <si>
+    <t>TC_NB_03_03</t>
+  </si>
+  <si>
+    <t>Validate user cannot proceed when only some mandatory fields are filled</t>
+  </si>
+  <si>
+    <t>1. Enter Flat No: 12B
+ 2. Leave Landmark and Save As Home(default)
+ 3. Click Proceed</t>
+  </si>
+  <si>
+    <t>Flat No: 12B | Landmark: blank | Save As: blank</t>
+  </si>
+  <si>
+    <t>Validation error shown on empty fields; user cannot proceed until all three fields are filled</t>
+  </si>
+  <si>
+    <t>TC_NB_03_04</t>
+  </si>
+  <si>
+    <t>Validate user proceeds successfully after filling all three fields</t>
+  </si>
+  <si>
+    <t>1. Enter Flat No: 12B
+ 2. Enter Landmark: Near Metro Station
+ 3. Select Save As: Home
+ 4. Click Proceed</t>
+  </si>
+  <si>
+    <t>Flat No: 12B | Landmark: Near Metro Station | Save As: Home</t>
+  </si>
+  <si>
+    <t>Address saved successfully; user navigates to date and time slot selection page</t>
+  </si>
+  <si>
+    <t>User navigates to date and time slot selection page with Address saved successfully</t>
+  </si>
+  <si>
+    <t>TC_NB_04_01</t>
+  </si>
+  <si>
+    <t>User has entered address and clicked Proceed</t>
+  </si>
+  <si>
+    <t>Validate only present and future dates are selectable on the calendar</t>
+  </si>
+  <si>
+    <t>1. On the Schedule Your Service Page, select Pick Date in Select Date
+ 2. Attempt to select today's date or a future date
+ 3. Observe which date is enabled</t>
+  </si>
+  <si>
+    <t>Date: Tomorrow</t>
+  </si>
+  <si>
+    <t>Tomorrow's date is selectable; past dates are greyed out and unclickable</t>
+  </si>
+  <si>
+    <t>TC_NB_04_02</t>
+  </si>
+  <si>
+    <t>User is on the Schedule your Service page</t>
+  </si>
+  <si>
+    <t>Validate available time slots are displayed upon selecting a valid date</t>
+  </si>
+  <si>
+    <t>1. Click on a valid future date on the calendar
+ 2. Observe time slots displayed below</t>
+  </si>
+  <si>
+    <t>Available time slots load for the selected date; user can click on a slot to select it</t>
+  </si>
+  <si>
+    <t>TC_NB_04_03</t>
+  </si>
+  <si>
+    <t>Validate user cannot proceed without selecting both date and time slot</t>
+  </si>
+  <si>
+    <t>1. Select a date but do not select any time slot
+ 2. Click Proceed/Next</t>
+  </si>
+  <si>
+    <t>Date: Selected | Slot: Not selected</t>
+  </si>
+  <si>
+    <t>Proceed button remains disabled ; user cannot move forward without selecting a time slot</t>
+  </si>
+  <si>
+    <t>Proceed button remains visible</t>
+  </si>
+  <si>
+    <t>TC_NB_04_04</t>
+  </si>
+  <si>
+    <t>User is on the Schedule Your Service page</t>
+  </si>
+  <si>
+    <t>Validate that a fully booked date displays an appropriate unavailability message</t>
+  </si>
+  <si>
+    <t>1.Click on Pick Date
+2.Select a date that is fully booked due to high demand
+3.Observe the message displayed on the screen</t>
+  </si>
+  <si>
+    <t>Date: A date with no available slots due to high demand</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>The message "Fully booked for the day due to high demand. Please choose another date." is displayed and no time slots are shown for that date. User is prompted to select a different date</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>The message "Fully booked for the day due to high demand. Please choose another date." is displayed and no time slots are shown for that date</t>
+  </si>
+  <si>
+    <t>TC_NB_05_01</t>
+  </si>
+  <si>
+    <t>User has completed service selection, address and slot selection</t>
+  </si>
+  <si>
+    <t>Validate order summary shows correct service, address, date, time and price</t>
+  </si>
+  <si>
+    <t>1. Reach the order summary page
+ 2. Verify service name, address, selected date, time slot and price displayed</t>
+  </si>
+  <si>
+    <t>Service: Fan Installation | Address: 12B, Indiranagar | Date: Tomorrow | Slot: 10AM-10:30AM</t>
+  </si>
+  <si>
+    <t>All details on summary page match the inputs provided in previous steps</t>
+  </si>
+  <si>
+    <t>TC_NB_05_02</t>
+  </si>
+  <si>
+    <t>User is on the order summary page</t>
+  </si>
+  <si>
+    <t>Validate price breakdown is transparent with no hidden charges</t>
+  </si>
+  <si>
+    <t>1. On the summary page, check the price section
+ 2. Verify itemised pricing is shown</t>
+  </si>
+  <si>
+    <t>Price breakdown shows base price, applicable taxes and convinience fees; no unexpected charges appear</t>
+  </si>
+  <si>
+    <t>Price breakdown shows base price, applicable taxes and convinience fees with the total amount below</t>
+  </si>
+  <si>
+    <t>TC_NB_05_03</t>
+  </si>
+  <si>
+    <t>Validate user can edit service or address from summary page</t>
+  </si>
+  <si>
+    <t>1. Click Add/Remove Items option in the Order Summary
+ 2. Add another service
+ 3. Click on Proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added Service: Socket Replacement </t>
+  </si>
+  <si>
+    <t>Summary updates correctly with the new service after edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User has to go through the date and slot selection again. Clicking on Procced navigates to the edited Order Summary page </t>
+  </si>
+  <si>
+    <t>TC_NB_05_04</t>
+  </si>
+  <si>
+    <t>User is on the booking summary page</t>
+  </si>
+  <si>
+    <t>Validate clicking Pay Now navigates to the Payment Portal</t>
+  </si>
+  <si>
+    <t>1. Review the booking summary
+ 2. Click 'Pay Now' button
+ 3. Observe the page that loads</t>
+  </si>
+  <si>
+    <t>User is navigated to the Payment Portal page showing available payment options (UPI, Card, Net Banking)</t>
+  </si>
+  <si>
+    <t>User is navigated to the Payment Portal Page</t>
+  </si>
+  <si>
+    <t>Defect Id.</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Defect Summary</t>
+  </si>
+  <si>
+    <t>Defect Priority</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>DF_NB_01</t>
+  </si>
+  <si>
+    <t>Home Services – Navigation</t>
+  </si>
+  <si>
+    <t>Homepage navigation label is misleading – 'Painting &amp; Cleaning' option redirects to the full Home Services landing page which includes unrelated services like Electrician, Plumber and Carpenter. No dedicated 'Home Services' label exists on the homepage.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>BR_ID</t>
+  </si>
+  <si>
+    <t>TR_ID</t>
+  </si>
+  <si>
+    <t>TS_ID</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DR_ID</t>
+  </si>
+  <si>
+    <t>BR_NB_01</t>
+  </si>
+  <si>
+    <t>TR_NB_01</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>BR_NB_02</t>
+  </si>
+  <si>
+    <t>TR_NB_02</t>
+  </si>
+  <si>
+    <t>BR_NB_03</t>
+  </si>
+  <si>
+    <t>TR_NB_03</t>
+  </si>
+  <si>
+    <t>BR_NB_04</t>
+  </si>
+  <si>
+    <t>TR_NB_04</t>
+  </si>
+  <si>
+    <t>BR_NB_05</t>
+  </si>
+  <si>
+    <t>TR_NB_05</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Fail Percentage</t>
+  </si>
+  <si>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>NoBroker Home Services</t>
+  </si>
+  <si>
+    <t>Homepage Navigation</t>
+  </si>
+  <si>
+    <t>Service Selection</t>
+  </si>
+  <si>
+    <t>Address Entry &amp; Validation</t>
+  </si>
+  <si>
+    <t>Date &amp; Time Slot Selection</t>
+  </si>
+  <si>
+    <t>Booking Summary &amp; Payment</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -318,8 +908,42 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,8 +992,38 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC65911"/>
+        <bgColor rgb="FFC65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+        <bgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B942"/>
+        <bgColor rgb="FFF4B942"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -385,11 +1039,41 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -429,6 +1113,86 @@
     </xf>
     <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf quotePrefix="1" borderId="1" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="13" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,6 +1207,22 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1159,7 +1939,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="13">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>74</v>
@@ -1188,4 +1968,1384 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="41.63"/>
+    <col customWidth="1" min="4" max="4" width="49.0"/>
+    <col customWidth="1" min="5" max="5" width="50.13"/>
+    <col customWidth="1" min="6" max="6" width="41.63"/>
+    <col customWidth="1" min="7" max="7" width="83.5"/>
+    <col customWidth="1" min="8" max="8" width="38.88"/>
+    <col customWidth="1" min="9" max="9" width="18.13"/>
+    <col customWidth="1" min="10" max="10" width="26.5"/>
+    <col customWidth="1" min="11" max="11" width="17.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" ht="27.0" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="18"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="18"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" s="18"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="59.38"/>
+    <col customWidth="1" min="3" max="3" width="58.25"/>
+    <col customWidth="1" min="4" max="4" width="24.5"/>
+    <col customWidth="1" min="5" max="5" width="24.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" ht="78.75" customHeight="1">
+      <c r="A2" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="24.0"/>
+    <col customWidth="1" min="2" max="2" width="21.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="D3" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="E3" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="G3" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="H3" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="37">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38"/>
+      <c r="B4" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C4" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="D4" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="E4" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="32">
+        <v>5.0</v>
+      </c>
+      <c r="G4" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="37">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38"/>
+      <c r="B5" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="D5" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="G5" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="37">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38"/>
+      <c r="B6" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="D6" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="E6" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="G6" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="37">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39"/>
+      <c r="B7" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="D7" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="E7" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="32">
+        <v>4.0</v>
+      </c>
+      <c r="G7" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="37">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40"/>
+      <c r="B8" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="D8" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="E8" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="G8" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>1.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A7"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>